--- a/examples/irs/Optima_IRS_Test_Case_Inputs_v4.xlsx
+++ b/examples/irs/Optima_IRS_Test_Case_Inputs_v4.xlsx
@@ -9,6 +9,10 @@
   </bookViews>
   <sheets>
     <sheet name="TC001" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="TC003" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="TC004" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="TC006" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="TC010" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -41,8 +45,96 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B62" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Relative path reference only; does not verify that folder/files exist.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B62" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Relative path reference only; does not verify that folder/files exist.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B62" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Relative path reference only; does not verify that folder/files exist.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B62" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Relative path reference only; does not verify that folder/files exist.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="102">
   <si>
     <t xml:space="preserve">OPTIMA | IRS TEST CASE INPUTS</t>
   </si>
@@ -309,6 +401,45 @@
   </si>
   <si>
     <t xml:space="preserve">Interpolation of the prepared snapshot; checked against it, never applied.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLLSL90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semiannual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLLSL9RX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quarterly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fixings_2026-03-31.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLLSL9SC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JPY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACT/365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TONAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JPY TONAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jpy_tona_2026-03-31.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLLSL9SF</t>
   </si>
 </sst>
 </file>
@@ -487,12 +618,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -500,7 +635,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -536,7 +671,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -808,750 +943,750 @@
   <dimension ref="A1:H66"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="32"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="6"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <v>530000</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="9" t="n">
         <v>46173</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="9" t="n">
         <v>46721</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="9" t="n">
         <v>46112</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B24" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="10" t="n">
+      <c r="B25" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="7" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-    </row>
-    <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D30" s="6"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B32" s="11" t="n">
+      <c r="B32" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6" t="s">
+      <c r="C32" s="7"/>
+      <c r="D32" s="7" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D33" s="6"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+      <c r="D33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B34" s="11" t="n">
+      <c r="B34" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6" t="s">
+      <c r="C34" s="7"/>
+      <c r="D34" s="7" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-    </row>
-    <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D40" s="6"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="12" t="s">
+      <c r="D40" s="7"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-    </row>
-    <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="13" t="s">
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+    </row>
+    <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E43" s="13" t="s">
+      <c r="E43" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="13" t="s">
+      <c r="F43" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G43" s="13" t="s">
+      <c r="G43" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="H43" s="13" t="s">
+      <c r="H43" s="14" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="n">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B44" s="8" t="n">
+      <c r="B44" s="9" t="n">
         <v>46173</v>
       </c>
-      <c r="C44" s="8" t="n">
+      <c r="C44" s="9" t="n">
         <v>46535</v>
       </c>
-      <c r="D44" s="8" t="n">
+      <c r="D44" s="9" t="n">
         <v>46535</v>
       </c>
-      <c r="E44" s="7" t="n">
+      <c r="E44" s="8" t="n">
         <v>530000</v>
       </c>
-      <c r="F44" s="14"/>
-      <c r="G44" s="7" t="n">
+      <c r="F44" s="15"/>
+      <c r="G44" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="5"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="n">
+      <c r="H44" s="6"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B45" s="8" t="n">
+      <c r="B45" s="9" t="n">
         <v>46535</v>
       </c>
-      <c r="C45" s="8" t="n">
+      <c r="C45" s="9" t="n">
         <v>46721</v>
       </c>
-      <c r="D45" s="8" t="n">
+      <c r="D45" s="9" t="n">
         <v>46721</v>
       </c>
-      <c r="E45" s="7" t="n">
+      <c r="E45" s="8" t="n">
         <v>265000</v>
       </c>
-      <c r="F45" s="14"/>
-      <c r="G45" s="7" t="n">
+      <c r="F45" s="15"/>
+      <c r="G45" s="8" t="n">
         <v>265000</v>
       </c>
-      <c r="H45" s="5"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="n">
+      <c r="H45" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="5"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="n">
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="6"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="5"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="n">
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="5"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="n">
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="6"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="5"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="n">
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="6"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="5"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="n">
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="6"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="5"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="n">
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="6"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="5"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="n">
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="6"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="5"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="n">
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="6"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="5"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="n">
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="6"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="5"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6" t="n">
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="6"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="5"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="n">
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="6"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="5"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6" t="n">
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="6"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="5"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3" t="s">
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="6"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D61" s="6"/>
-    </row>
-    <row r="62" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="s">
+      <c r="D61" s="7"/>
+    </row>
+    <row r="62" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B62" s="15" t="str">
+      <c r="B62" s="16" t="str">
         <f aca="false">IF(OR(B10="",B6=""),"","market_data/"&amp;TEXT(B10,"yyyy-mm-dd")&amp;"/"&amp;B6&amp;"/")</f>
         <v>market_data/2026-03-31/USD/</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D62" s="6" t="s">
+      <c r="D62" s="7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="s">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D63" s="6"/>
-    </row>
-    <row r="64" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="s">
+      <c r="D63" s="7"/>
+    </row>
+    <row r="64" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B64" s="5"/>
-      <c r="C64" s="6" t="s">
+      <c r="B64" s="6"/>
+      <c r="C64" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D64" s="6"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
+      <c r="D64" s="7"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B65" s="8"/>
-      <c r="C65" s="6" t="s">
+      <c r="B65" s="9"/>
+      <c r="C65" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="D65" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
+    <row r="66" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D66" s="6"/>
+      <c r="D66" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1655,4 +1790,3500 @@
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF17365D"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:H66"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="32"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>790000</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>46173</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>46873</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D40" s="7"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+    </row>
+    <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" s="9" t="n">
+        <v>46173</v>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>46356</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>46356</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>790000</v>
+      </c>
+      <c r="F44" s="15"/>
+      <c r="G44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="6"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>46356</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>46535</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>46535</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>592500</v>
+      </c>
+      <c r="F45" s="15"/>
+      <c r="G45" s="8" t="n">
+        <v>197500</v>
+      </c>
+      <c r="H45" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>46535</v>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>46721</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>46721</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>395000</v>
+      </c>
+      <c r="F46" s="15"/>
+      <c r="G46" s="8" t="n">
+        <v>197500</v>
+      </c>
+      <c r="H46" s="6"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>46721</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>46871</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>46871</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>197500</v>
+      </c>
+      <c r="F47" s="15"/>
+      <c r="G47" s="8" t="n">
+        <v>197500</v>
+      </c>
+      <c r="H47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="6"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="6"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="6"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="6"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="6"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="6"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="6"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="6"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="6"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="6"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="6"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D61" s="7"/>
+    </row>
+    <row r="62" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B62" s="16" t="str">
+        <f aca="false">IF(OR(B10="",B6=""),"","market_data/"&amp;TEXT(B10,"yyyy-mm-dd")&amp;"/"&amp;B6&amp;"/")</f>
+        <v>market_data/2026-03-31/USD/</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D63" s="7"/>
+    </row>
+    <row r="64" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B64" s="6"/>
+      <c r="C64" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D64" s="7"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B65" s="9"/>
+      <c r="C65" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D66" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A60:H60"/>
+  </mergeCells>
+  <dataValidations count="20">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B33" type="list">
+      <formula1>"Lookback"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B6" type="list">
+      <formula1>"USD,CHF,JPY,INR"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B13" type="list">
+      <formula1>"Pay,Receive"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B15" type="list">
+      <formula1>"Annual,Semiannual,Quarterly,Monthly"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B16" type="list">
+      <formula1>"ACT/360,ACT/365,30/360"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B17" type="list">
+      <formula1>"Modified Following,Following,Preceding,Unadjusted"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B21" type="list">
+      <formula1>"Pay,Receive"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B22" type="list">
+      <formula1>"SOFR,SARON,TONAR,INR OIS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B23" type="list">
+      <formula1>"1D,6M,3M,1Y"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B26" type="list">
+      <formula1>"Daily,Monthly,Quarterly,Semiannual,Annual"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B27" type="list">
+      <formula1>"Annual,Semiannual,Quarterly,Monthly"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B28" type="list">
+      <formula1>"ACT/360,ACT/365,30/360"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B31" type="list">
+      <formula1>"In Arrears,In Advance"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B35" type="list">
+      <formula1>"Daily Compounded,Simple"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B36" type="list">
+      <formula1>"Exclude Spread,Compound Spread"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B39" type="list">
+      <formula1>"Never,At Start,At End,Start &amp; End"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B40" type="list">
+      <formula1>"Custom Schedule,Percentage per Period,Bullet / No Amortisation"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B61" type="list">
+      <formula1>"USD SOFR,CHF SARON,JPY TONAR,INR OIS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B66" type="list">
+      <formula1>"Log Linear,Linear,Piecewise Linear (Cont)"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B29" type="list">
+      <formula1>"Modified Following,Following,Preceding,Unadjusted"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF17365D"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:H66"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="32"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>930000</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>46446</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D40" s="7"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+    </row>
+    <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" s="9" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>46112</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>930000</v>
+      </c>
+      <c r="F44" s="15"/>
+      <c r="G44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="6"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>744000</v>
+      </c>
+      <c r="F45" s="15"/>
+      <c r="G45" s="8" t="n">
+        <v>186000</v>
+      </c>
+      <c r="H45" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>558000</v>
+      </c>
+      <c r="F46" s="15"/>
+      <c r="G46" s="8" t="n">
+        <v>186000</v>
+      </c>
+      <c r="H46" s="6"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>46387</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>46387</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>372000</v>
+      </c>
+      <c r="F47" s="15"/>
+      <c r="G47" s="8" t="n">
+        <v>186000</v>
+      </c>
+      <c r="H47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B48" s="9" t="n">
+        <v>46387</v>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>46444</v>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>46444</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>186000</v>
+      </c>
+      <c r="F48" s="15"/>
+      <c r="G48" s="8" t="n">
+        <v>186000</v>
+      </c>
+      <c r="H48" s="6"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="6"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="6"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="6"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="6"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="6"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="6"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="6"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="6"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="6"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="6"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D61" s="7"/>
+    </row>
+    <row r="62" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B62" s="16" t="str">
+        <f aca="false">IF(OR(B10="",B6=""),"","market_data/"&amp;TEXT(B10,"yyyy-mm-dd")&amp;"/"&amp;B6&amp;"/")</f>
+        <v>market_data/2026-03-31/USD/</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D63" s="7"/>
+    </row>
+    <row r="64" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D64" s="7"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B65" s="9"/>
+      <c r="C65" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D66" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A60:H60"/>
+  </mergeCells>
+  <dataValidations count="20">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B33" type="list">
+      <formula1>"Lookback"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B6" type="list">
+      <formula1>"USD,CHF,JPY,INR"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B13" type="list">
+      <formula1>"Pay,Receive"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B15" type="list">
+      <formula1>"Annual,Semiannual,Quarterly,Monthly"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B16" type="list">
+      <formula1>"ACT/360,ACT/365,30/360"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B17" type="list">
+      <formula1>"Modified Following,Following,Preceding,Unadjusted"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B21" type="list">
+      <formula1>"Pay,Receive"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B22" type="list">
+      <formula1>"SOFR,SARON,TONAR,INR OIS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B23" type="list">
+      <formula1>"1D,6M,3M,1Y"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B26" type="list">
+      <formula1>"Daily,Monthly,Quarterly,Semiannual,Annual"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B27" type="list">
+      <formula1>"Annual,Semiannual,Quarterly,Monthly"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B28" type="list">
+      <formula1>"ACT/360,ACT/365,30/360"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B31" type="list">
+      <formula1>"In Arrears,In Advance"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B35" type="list">
+      <formula1>"Daily Compounded,Simple"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B36" type="list">
+      <formula1>"Exclude Spread,Compound Spread"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B39" type="list">
+      <formula1>"Never,At Start,At End,Start &amp; End"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B40" type="list">
+      <formula1>"Custom Schedule,Percentage per Period,Bullet / No Amortisation"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B61" type="list">
+      <formula1>"USD SOFR,CHF SARON,JPY TONAR,INR OIS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B66" type="list">
+      <formula1>"Log Linear,Linear,Piecewise Linear (Cont)"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B29" type="list">
+      <formula1>"Modified Following,Following,Preceding,Unadjusted"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF17365D"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:H66"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="32"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>7300000</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>46783</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D40" s="7"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+    </row>
+    <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" s="9" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>46416</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>46416</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>7300000</v>
+      </c>
+      <c r="F44" s="15"/>
+      <c r="G44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="6"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>46416</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>46598</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>46598</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>4866666.67</v>
+      </c>
+      <c r="F45" s="15"/>
+      <c r="G45" s="8" t="n">
+        <v>2433333.33</v>
+      </c>
+      <c r="H45" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>46598</v>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>46783</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>46783</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>2433333.34</v>
+      </c>
+      <c r="F46" s="15"/>
+      <c r="G46" s="8" t="n">
+        <v>2433333.33</v>
+      </c>
+      <c r="H46" s="6"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="6"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="6"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="6"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="6"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="6"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="6"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="6"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="6"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="6"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="6"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="6"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D61" s="7"/>
+    </row>
+    <row r="62" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B62" s="16" t="str">
+        <f aca="false">IF(OR(B10="",B6=""),"","market_data/"&amp;TEXT(B10,"yyyy-mm-dd")&amp;"/"&amp;B6&amp;"/")</f>
+        <v>market_data/2026-03-31/JPY/</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D63" s="7"/>
+    </row>
+    <row r="64" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B64" s="6"/>
+      <c r="C64" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D64" s="7"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B65" s="9"/>
+      <c r="C65" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D66" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A60:H60"/>
+  </mergeCells>
+  <dataValidations count="20">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B33" type="list">
+      <formula1>"Lookback"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B6" type="list">
+      <formula1>"USD,CHF,JPY,INR"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B13" type="list">
+      <formula1>"Pay,Receive"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B15" type="list">
+      <formula1>"Annual,Semiannual,Quarterly,Monthly"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B16" type="list">
+      <formula1>"ACT/360,ACT/365,30/360"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B17" type="list">
+      <formula1>"Modified Following,Following,Preceding,Unadjusted"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B21" type="list">
+      <formula1>"Pay,Receive"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B22" type="list">
+      <formula1>"SOFR,SARON,TONAR,INR OIS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B23" type="list">
+      <formula1>"1D,6M,3M,1Y"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B26" type="list">
+      <formula1>"Daily,Monthly,Quarterly,Semiannual,Annual"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B27" type="list">
+      <formula1>"Annual,Semiannual,Quarterly,Monthly"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B28" type="list">
+      <formula1>"ACT/360,ACT/365,30/360"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B31" type="list">
+      <formula1>"In Arrears,In Advance"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B35" type="list">
+      <formula1>"Daily Compounded,Simple"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B36" type="list">
+      <formula1>"Exclude Spread,Compound Spread"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B39" type="list">
+      <formula1>"Never,At Start,At End,Start &amp; End"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B40" type="list">
+      <formula1>"Custom Schedule,Percentage per Period,Bullet / No Amortisation"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B61" type="list">
+      <formula1>"USD SOFR,CHF SARON,JPY TONAR,INR OIS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B66" type="list">
+      <formula1>"Log Linear,Linear,Piecewise Linear (Cont)"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B29" type="list">
+      <formula1>"Modified Following,Following,Preceding,Unadjusted"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF17365D"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:H66"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="32"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>54400000</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>46568</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D40" s="7"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+    </row>
+    <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" s="9" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>46477</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>46477</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>54400000</v>
+      </c>
+      <c r="F44" s="15"/>
+      <c r="G44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="6"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>46477</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>46568</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>27200000</v>
+      </c>
+      <c r="F45" s="15"/>
+      <c r="G45" s="8" t="n">
+        <v>27200000</v>
+      </c>
+      <c r="H45" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="6"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="6"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="6"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="6"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="6"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="6"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="6"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="6"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="6"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="6"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="6"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="6"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D61" s="7"/>
+    </row>
+    <row r="62" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B62" s="16" t="str">
+        <f aca="false">IF(OR(B10="",B6=""),"","market_data/"&amp;TEXT(B10,"yyyy-mm-dd")&amp;"/"&amp;B6&amp;"/")</f>
+        <v>market_data/2026-03-31/JPY/</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D63" s="7"/>
+    </row>
+    <row r="64" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D64" s="7"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B65" s="9"/>
+      <c r="C65" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D66" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A60:H60"/>
+  </mergeCells>
+  <dataValidations count="20">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B33" type="list">
+      <formula1>"Lookback"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B6" type="list">
+      <formula1>"USD,CHF,JPY,INR"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B13" type="list">
+      <formula1>"Pay,Receive"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B15" type="list">
+      <formula1>"Annual,Semiannual,Quarterly,Monthly"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B16" type="list">
+      <formula1>"ACT/360,ACT/365,30/360"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B17" type="list">
+      <formula1>"Modified Following,Following,Preceding,Unadjusted"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B21" type="list">
+      <formula1>"Pay,Receive"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B22" type="list">
+      <formula1>"SOFR,SARON,TONAR,INR OIS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B23" type="list">
+      <formula1>"1D,6M,3M,1Y"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B26" type="list">
+      <formula1>"Daily,Monthly,Quarterly,Semiannual,Annual"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B27" type="list">
+      <formula1>"Annual,Semiannual,Quarterly,Monthly"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B28" type="list">
+      <formula1>"ACT/360,ACT/365,30/360"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B31" type="list">
+      <formula1>"In Arrears,In Advance"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B35" type="list">
+      <formula1>"Daily Compounded,Simple"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B36" type="list">
+      <formula1>"Exclude Spread,Compound Spread"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B39" type="list">
+      <formula1>"Never,At Start,At End,Start &amp; End"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B40" type="list">
+      <formula1>"Custom Schedule,Percentage per Period,Bullet / No Amortisation"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B61" type="list">
+      <formula1>"USD SOFR,CHF SARON,JPY TONAR,INR OIS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B66" type="list">
+      <formula1>"Log Linear,Linear,Piecewise Linear (Cont)"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B29" type="list">
+      <formula1>"Modified Following,Following,Preceding,Unadjusted"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>